--- a/price_report.xlsx
+++ b/price_report.xlsx
@@ -459,7 +459,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -489,7 +489,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -517,7 +517,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
